--- a/resources/excel_tables/map.xlsx
+++ b/resources/excel_tables/map.xlsx
@@ -1,21 +1,137 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" tabRatio="600" autoFilterDateGrouping="true"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1" state="visible"/>
+    <sheet name="Maps" sheetId="2" r:id="rId4"/>
+    <sheet name="SpawnPoints" sheetId="3" r:id="rId5"/>
+    <sheet name="TeleportPoints" sheetId="4" r:id="rId7"/>
+    <sheet name="Buildings" sheetId="5" r:id="rId8"/>
+    <sheet name="Events" sheetId="6" r:id="rId9"/>
+    <sheet name="Resources" sheetId="7" r:id="rId10"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>MapID</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>ObjectID</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Frequency</t>
+  </si>
+  <si>
+    <t>GroupID</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>TargetMapID</t>
+  </si>
+  <si>
+    <t>TargetX</t>
+  </si>
+  <si>
+    <t>TargetY</t>
+  </si>
+  <si>
+    <t>TargetZ</t>
+  </si>
+  <si>
+    <t>RequiredLevel</t>
+  </si>
+  <si>
+    <t>RequiredItem</t>
+  </si>
+  <si>
+    <t>IsActive</t>
+  </si>
+  <si>
+    <t>Width</t>
+  </si>
+  <si>
+    <t>Height</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>Faction</t>
+  </si>
+  <si>
+    <t>EventID</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Radius</t>
+  </si>
+  <si>
+    <t>StartTime</t>
+  </si>
+  <si>
+    <t>EndTime</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>RewardID</t>
+  </si>
+  <si>
+    <t>ResourceID</t>
+  </si>
+  <si>
+    <t>RespawnTime</t>
+  </si>
+  <si>
+    <t>ItemID</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>IsGathering</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <numFmts count="0"/>
   <fonts count="1">
     <font>
@@ -47,12 +163,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="false" pivotButton="false"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="false"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -125,7 +241,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -408,9 +524,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:R26"/>
@@ -2211,4 +2327,2043 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>MapID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>MapType</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>RegionSize</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>TileWidth</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>TileHeight</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>IsInstance</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>MaxPlayers</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Background</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>WeatherType</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>MinLevel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>MaxLevel</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>RespawnRate</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>json_file</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>青竹村</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>200</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>东胜州的新手村，竹林环绕，宁静祥和的小村庄</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>qing_zhu_village_bg.jpg</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>qing_zhu_village.mp3</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>sunny</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>dong_sheng_qing_zhu_village.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1002</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>青竹山</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>800</v>
+      </c>
+      <c r="E3" t="n">
+        <v>800</v>
+      </c>
+      <c r="F3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>300</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>东胜州的野外地图，竹林茂密，盛产竹笋和灵竹</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>qing_zhu_mountain_bg.jpg</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>qing_zhu_mountain.mp3</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>sunny</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>5</v>
+      </c>
+      <c r="P3" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>dong_sheng_qing_zhu_mountain.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1003</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>东海之滨</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>800</v>
+      </c>
+      <c r="F4" t="n">
+        <v>50</v>
+      </c>
+      <c r="G4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>300</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>东胜州的野外地图，沙滩广阔，时有海妖出没</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>east_sea_coast_bg.jpg</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>east_sea_coast.mp3</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>sunny</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>10</v>
+      </c>
+      <c r="P4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>dong_sheng_east_sea_coast.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1004</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>剑冢</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>600</v>
+      </c>
+      <c r="E5" t="n">
+        <v>600</v>
+      </c>
+      <c r="F5" t="n">
+        <v>50</v>
+      </c>
+      <c r="G5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>50</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>东胜州的地下城，古代剑修的埋骨之地，藏有上古剑器</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>sword_tomb_bg.jpg</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>sword_tomb.mp3</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>dark</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>15</v>
+      </c>
+      <c r="P5" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>dong_sheng_sword_tomb.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1005</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>剑华城</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>500</v>
+      </c>
+      <c r="F6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>500</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>以剑为尊的城市，建筑多为剑形设计，是东胜州的主城。</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>sword_city_bg.jpg</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>sword_city.mp3</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>sunny</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>10</v>
+      </c>
+      <c r="P6" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>dong_sheng_sword_city.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>苗寨</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>500</v>
+      </c>
+      <c r="F7" t="n">
+        <v>50</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>200</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>南荒州的新手村，吊脚楼风格的村落，周围环绕毒藤</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>miao_village_bg.jpg</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>miao_village.mp3</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>sunny</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>nan_huang_miao_village.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>毒瘴林</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>800</v>
+      </c>
+      <c r="E8" t="n">
+        <v>800</v>
+      </c>
+      <c r="F8" t="n">
+        <v>50</v>
+      </c>
+      <c r="G8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>300</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>南荒州的野外地图，瘴气弥漫，毒虫遍布</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>poison_forest_bg.jpg</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>poison_forest.mp3</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>foggy</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>nan_huang_poison_forest.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>火炎谷</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E9" t="n">
+        <v>800</v>
+      </c>
+      <c r="F9" t="n">
+        <v>50</v>
+      </c>
+      <c r="G9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>300</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>南荒州的野外地图，地热活跃，盛产火属性灵物</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>fire_valley_bg.jpg</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>fire_valley.mp3</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>hot</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>10</v>
+      </c>
+      <c r="P9" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>nan_huang_fire_valley.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>蛊王洞</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>600</v>
+      </c>
+      <c r="E10" t="n">
+        <v>600</v>
+      </c>
+      <c r="F10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>南荒州的地下城，蛊师圣地，蛊王居住之地</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>gu_king_cave_bg.jpg</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>gu_king_cave.mp3</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>dark</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>15</v>
+      </c>
+      <c r="P10" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>nan_huang_gu_king_cave.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>万蛊城</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F11" t="n">
+        <v>50</v>
+      </c>
+      <c r="G11" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>500</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>南荒州的主城，以蛊术闻名，建筑多为圆形，象征蛊卵</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>ten_thousand_gu_city_bg.jpg</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ten_thousand_gu_city.mp3</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>sunny</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>20</v>
+      </c>
+      <c r="P11" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>nan_huang_ten_thousand_gu_city.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3001</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>沙枣村</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>500</v>
+      </c>
+      <c r="E12" t="n">
+        <v>500</v>
+      </c>
+      <c r="F12" t="n">
+        <v>50</v>
+      </c>
+      <c r="G12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>200</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>西凉州的新手村，位于沙漠边缘，以沙枣树闻名的小村庄</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>sand_date_village_bg.jpg</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>sand_date_village.mp3</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>sunny</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>xi_liang_sand_date_village.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3002</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>流沙之漠</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>800</v>
+      </c>
+      <c r="E13" t="n">
+        <v>800</v>
+      </c>
+      <c r="F13" t="n">
+        <v>50</v>
+      </c>
+      <c r="G13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>300</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>西凉州的野外地图1，广阔的沙漠地带，流沙陷阱众多</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>quicksand_desert_bg.jpg</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>quicksand_desert.mp3</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>sunny</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>5</v>
+      </c>
+      <c r="P13" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>xi_liang_quicksand_desert.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3003</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>月牙泉</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>800</v>
+      </c>
+      <c r="E14" t="n">
+        <v>800</v>
+      </c>
+      <c r="F14" t="n">
+        <v>50</v>
+      </c>
+      <c r="G14" t="n">
+        <v>10</v>
+      </c>
+      <c r="H14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>300</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>西凉州的野外地图2，沙漠中的绿洲，月牙形的泉水是其标志</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>crescent_spring_bg.jpg</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>crescent_spring.mp3</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>sunny</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>15</v>
+      </c>
+      <c r="P14" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>xi_liang_crescent_spring.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3004</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>蜃楼迷宫</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>600</v>
+      </c>
+      <c r="E15" t="n">
+        <v>600</v>
+      </c>
+      <c r="F15" t="n">
+        <v>50</v>
+      </c>
+      <c r="G15" t="n">
+        <v>10</v>
+      </c>
+      <c r="H15" t="n">
+        <v>10</v>
+      </c>
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>50</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>西凉州的地下城，由沙漠蜃气形成的迷宫，充满了幻象和宝藏</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>mirage_maze_bg.jpg</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>mirage_maze.mp3</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>foggy</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>20</v>
+      </c>
+      <c r="P15" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>xi_liang_mirage_maze.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3005</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>金沙城</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>500</v>
+      </c>
+      <c r="E16" t="n">
+        <v>500</v>
+      </c>
+      <c r="F16" t="n">
+        <v>50</v>
+      </c>
+      <c r="G16" t="n">
+        <v>10</v>
+      </c>
+      <c r="H16" t="n">
+        <v>10</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>500</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>西凉州的主城，由金沙建造，是沙漠中的贸易中心</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>golden_sand_city_bg.jpg</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>golden_sand_city.mp3</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>sunny</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>10</v>
+      </c>
+      <c r="P16" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>xi_liang_golden_sand_city.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>4001</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>雪狼村</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>500</v>
+      </c>
+      <c r="E17" t="n">
+        <v>500</v>
+      </c>
+      <c r="F17" t="n">
+        <v>50</v>
+      </c>
+      <c r="G17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H17" t="n">
+        <v>10</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>200</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>北寒州的新手村，位于雪原边缘，以雪狼为守护的小村庄</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>snow_wolf_village_bg.jpg</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>snow_wolf_village.mp3</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>snowy</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>bei_han_snow_wolf_village.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>4002</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>冰原</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>800</v>
+      </c>
+      <c r="E18" t="n">
+        <v>800</v>
+      </c>
+      <c r="F18" t="n">
+        <v>50</v>
+      </c>
+      <c r="G18" t="n">
+        <v>10</v>
+      </c>
+      <c r="H18" t="n">
+        <v>10</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>300</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>北寒州的野外地图1，广阔的冰原地带，冰风暴频繁</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>ice_plains_bg.jpg</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ice_plains.mp3</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>snowy</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>5</v>
+      </c>
+      <c r="P18" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>bei_han_ice_plains.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>4003</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>极光谷</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>800</v>
+      </c>
+      <c r="E19" t="n">
+        <v>800</v>
+      </c>
+      <c r="F19" t="n">
+        <v>50</v>
+      </c>
+      <c r="G19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" t="n">
+        <v>10</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>300</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>北寒州的野外地图2，极光笼罩的山谷，神秘而美丽</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>aurora_valley_bg.jpg</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>aurora_valley.mp3</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>snowy</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>15</v>
+      </c>
+      <c r="P19" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>bei_han_aurora_valley.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>4004</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>冰龙巢</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>600</v>
+      </c>
+      <c r="E20" t="n">
+        <v>600</v>
+      </c>
+      <c r="F20" t="n">
+        <v>50</v>
+      </c>
+      <c r="G20" t="n">
+        <v>10</v>
+      </c>
+      <c r="H20" t="n">
+        <v>10</v>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>50</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>北寒州的地下城，冰龙的巢穴，充满了冰元素和宝藏</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>ice_dragon_nest_bg.jpg</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>ice_dragon_nest.mp3</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>snowy</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>20</v>
+      </c>
+      <c r="P20" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>bei_han_ice_dragon_nest.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>4005</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>冰璃城</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>500</v>
+      </c>
+      <c r="E21" t="n">
+        <v>500</v>
+      </c>
+      <c r="F21" t="n">
+        <v>50</v>
+      </c>
+      <c r="G21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H21" t="n">
+        <v>10</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>500</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>北寒州的主城，由冰璃建造，是冰元素的聚集地</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>ice_crystal_city_bg.jpg</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>ice_crystal_city.mp3</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>snowy</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>10</v>
+      </c>
+      <c r="P21" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>bei_han_ice_crystal_city.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>5001</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>中央平原</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F22" t="n">
+        <v>50</v>
+      </c>
+      <c r="G22" t="n">
+        <v>10</v>
+      </c>
+      <c r="H22" t="n">
+        <v>10</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>500</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>中州的野外地图1，广阔的中央平原，连接着各个州的交通枢纽</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>central_plains_bg.jpg</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>central_plains.mp3</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>30</v>
+      </c>
+      <c r="P22" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>zhong_zhou_central_plains.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>5002</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>圣山</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>150</v>
+      </c>
+      <c r="E23" t="n">
+        <v>150</v>
+      </c>
+      <c r="F23" t="n">
+        <v>50</v>
+      </c>
+      <c r="G23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H23" t="n">
+        <v>10</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>500</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>大陆最高山峰，山顶有神秘宫殿，是中州的野外地图2。</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>default_bg.jpg</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>mountain</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>30</v>
+      </c>
+      <c r="P23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>zhong_zhou_sacred_mountain.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>5003</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>远古遗迹</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>150</v>
+      </c>
+      <c r="E24" t="n">
+        <v>150</v>
+      </c>
+      <c r="F24" t="n">
+        <v>50</v>
+      </c>
+      <c r="G24" t="n">
+        <v>10</v>
+      </c>
+      <c r="H24" t="n">
+        <v>10</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>500</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>上古文明的遗迹，藏有惊天秘密，是中州的地下城。</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>default_bg.jpg</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>ruins</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>30</v>
+      </c>
+      <c r="P24" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>zhong_zhou_ancient_ruins.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>5004</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>玄元城</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>200</v>
+      </c>
+      <c r="E25" t="n">
+        <v>200</v>
+      </c>
+      <c r="F25" t="n">
+        <v>50</v>
+      </c>
+      <c r="G25" t="n">
+        <v>10</v>
+      </c>
+      <c r="H25" t="n">
+        <v>10</v>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>500</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>大陆中心城市，建筑宏伟，汇聚四州风格，是中州的主城。</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>default_bg.jpg</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>central_city</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>sunny</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>30</v>
+      </c>
+      <c r="P25" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>zhong_zhou_xuan_yuan_city.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5005</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>跨服战场</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>200</v>
+      </c>
+      <c r="E26" t="n">
+        <v>200</v>
+      </c>
+      <c r="F26" t="n">
+        <v>50</v>
+      </c>
+      <c r="G26" t="n">
+        <v>10</v>
+      </c>
+      <c r="H26" t="n">
+        <v>10</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>500</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>服务器组内玩家可以在此争夺资源的跨服战场，是中州的特殊区域。</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>default_bg.jpg</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>battlefield</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>30</v>
+      </c>
+      <c r="P26" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>zhong_zhou_cross_server_battlefield.json</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:K1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:M1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:L1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:N1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:K1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>